--- a/bocfp-api/report/bocfp.xlsx
+++ b/bocfp-api/report/bocfp.xlsx
@@ -125,7 +125,19 @@
     <t>Date</t>
   </si>
   <si>
+    <t>User First Name</t>
+  </si>
+  <si>
+    <t>User Last Name</t>
+  </si>
+  <si>
     <t>Overweight</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>Bocfp</t>
   </si>
   <si>
     <t>Underweight</t>
@@ -344,6 +356,8 @@
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -371,6 +385,12 @@
       <c r="H1" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
@@ -389,13 +409,19 @@
         <v>79</v>
       </c>
       <c r="F2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G2">
         <v>27.66009593501628</v>
       </c>
       <c r="H2" s="2">
         <v>44964.27569444444</v>
+      </c>
+      <c r="I2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J2" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="3">
@@ -415,13 +441,19 @@
         <v>59</v>
       </c>
       <c r="F3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G3">
         <v>29.260067446935132</v>
       </c>
       <c r="H3" s="2">
         <v>44963.68262731482</v>
+      </c>
+      <c r="I3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="4">
@@ -441,13 +473,19 @@
         <v>45</v>
       </c>
       <c r="F4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G4">
         <v>17.578125</v>
       </c>
       <c r="H4" s="2">
         <v>44963.582083333335</v>
+      </c>
+      <c r="I4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="5">
@@ -467,13 +505,19 @@
         <v>45</v>
       </c>
       <c r="F5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G5">
         <v>19.47714681440443</v>
       </c>
       <c r="H5" s="2">
         <v>44961.76358796297</v>
+      </c>
+      <c r="I5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="6">
@@ -493,13 +537,19 @@
         <v>44</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G6">
         <v>15.967484395412978</v>
       </c>
       <c r="H6" s="2">
         <v>44961.76358796297</v>
+      </c>
+      <c r="I6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/bocfp-api/report/bocfp.xlsx
+++ b/bocfp-api/report/bocfp.xlsx
@@ -53,7 +53,7 @@
     <t>Father</t>
   </si>
   <si>
-    <t>Amir El</t>
+    <t>Amir el</t>
   </si>
   <si>
     <t>Amari</t>

--- a/bocfp-api/report/bocfp.xlsx
+++ b/bocfp-api/report/bocfp.xlsx
@@ -35,6 +35,42 @@
     <t>Relationship</t>
   </si>
   <si>
+    <t>Amir el</t>
+  </si>
+  <si>
+    <t>Amari</t>
+  </si>
+  <si>
+    <t>Jane</t>
+  </si>
+  <si>
+    <t>Doe</t>
+  </si>
+  <si>
+    <t>AYPDCLM</t>
+  </si>
+  <si>
+    <t>Mother</t>
+  </si>
+  <si>
+    <t>Jock</t>
+  </si>
+  <si>
+    <t>Charlie</t>
+  </si>
+  <si>
+    <t>Hawk</t>
+  </si>
+  <si>
+    <t>Dough</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>Dummy</t>
+  </si>
+  <si>
     <t>Rebecca</t>
   </si>
   <si>
@@ -53,28 +89,10 @@
     <t>Father</t>
   </si>
   <si>
-    <t>Amir el</t>
-  </si>
-  <si>
-    <t>Amari</t>
-  </si>
-  <si>
-    <t>Jane</t>
-  </si>
-  <si>
-    <t>Doe</t>
-  </si>
-  <si>
-    <t>AYPDCLM</t>
-  </si>
-  <si>
-    <t>Mother</t>
-  </si>
-  <si>
-    <t>Jock</t>
-  </si>
-  <si>
-    <t>Charlie</t>
+    <t>Zed</t>
+  </si>
+  <si>
+    <t>Shadow</t>
   </si>
   <si>
     <t>Shen</t>
@@ -90,24 +108,6 @@
   </si>
   <si>
     <t>MRN5K5A</t>
-  </si>
-  <si>
-    <t>Hawk</t>
-  </si>
-  <si>
-    <t>Dough</t>
-  </si>
-  <si>
-    <t>Zed</t>
-  </si>
-  <si>
-    <t>Shadow</t>
-  </si>
-  <si>
-    <t>Test</t>
-  </si>
-  <si>
-    <t>Dummy</t>
   </si>
   <si>
     <t>Height</t>
@@ -228,7 +228,7 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
@@ -251,98 +251,98 @@
         <v>14</v>
       </c>
       <c r="C3">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C7">
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" t="s">
         <v>30</v>
       </c>
-      <c r="B8" t="s">
+      <c r="F8" t="s">
         <v>31</v>
       </c>
-      <c r="C8">
-        <v>3</v>
+      <c r="G8" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -400,22 +400,22 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D2">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="E2">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="F2" t="s">
         <v>39</v>
       </c>
       <c r="G2">
-        <v>27.66009593501628</v>
+        <v>29.260067446935132</v>
       </c>
       <c r="H2" s="2">
-        <v>44964.27569444444</v>
+        <v>44963.68262731482</v>
       </c>
       <c r="I2" t="s">
         <v>40</v>
@@ -432,22 +432,22 @@
         <v>14</v>
       </c>
       <c r="C3">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="E3">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G3">
-        <v>29.260067446935132</v>
+        <v>17.578125</v>
       </c>
       <c r="H3" s="2">
-        <v>44963.68262731482</v>
+        <v>44963.582083333335</v>
       </c>
       <c r="I3" t="s">
         <v>40</v>
@@ -464,22 +464,22 @@
         <v>20</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D4">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="E4">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="F4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G4">
-        <v>17.578125</v>
+        <v>27.66009593501628</v>
       </c>
       <c r="H4" s="2">
-        <v>44963.582083333335</v>
+        <v>44964.27569444444</v>
       </c>
       <c r="I4" t="s">
         <v>40</v>
@@ -490,25 +490,25 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C5">
         <v>6</v>
       </c>
       <c r="D5">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="E5">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G5">
-        <v>19.47714681440443</v>
+        <v>15.967484395412978</v>
       </c>
       <c r="H5" s="2">
         <v>44961.76358796297</v>
@@ -522,25 +522,25 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
         <v>28</v>
-      </c>
-      <c r="B6" t="s">
-        <v>29</v>
       </c>
       <c r="C6">
         <v>6</v>
       </c>
       <c r="D6">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="E6">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G6">
-        <v>15.967484395412978</v>
+        <v>19.47714681440443</v>
       </c>
       <c r="H6" s="2">
         <v>44961.76358796297</v>

--- a/bocfp-api/report/bocfp.xlsx
+++ b/bocfp-api/report/bocfp.xlsx
@@ -467,7 +467,7 @@
         <v>8</v>
       </c>
       <c r="D4">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E4">
         <v>79</v>
@@ -479,7 +479,7 @@
         <v>27.66009593501628</v>
       </c>
       <c r="H4" s="2">
-        <v>44964.27569444444</v>
+        <v>44969.3205787037</v>
       </c>
       <c r="I4" t="s">
         <v>40</v>

--- a/bocfp-api/report/bocfp.xlsx
+++ b/bocfp-api/report/bocfp.xlsx
@@ -134,6 +134,9 @@
     <t>Overweight</t>
   </si>
   <si>
+    <t>Feb 07, 2023 12:22 AM</t>
+  </si>
+  <si>
     <t>Admin</t>
   </si>
   <si>
@@ -141,6 +144,15 @@
   </si>
   <si>
     <t>Underweight</t>
+  </si>
+  <si>
+    <t>Feb 06, 2023 09:58 PM</t>
+  </si>
+  <si>
+    <t>Feb 12, 2023 03:41 PM</t>
+  </si>
+  <si>
+    <t>Feb 05, 2023 02:19 AM</t>
   </si>
   <si>
     <t>Normal</t>
@@ -150,9 +162,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="100" formatCode="MMM DD, YYYY hh:mm AM/PM"/>
-  </numFmts>
   <fonts count="2">
     <font>
       <sz val="12"/>
@@ -186,10 +195,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf/>
     <xf fontId="1" applyFont="1"/>
-    <xf numFmtId="100" applyNumberFormat="1"/>
   </cellXfs>
 </styleSheet>
 </file>
@@ -414,14 +422,14 @@
       <c r="G2">
         <v>29.260067446935132</v>
       </c>
-      <c r="H2" s="2">
-        <v>44963.68262731482</v>
+      <c r="H2" t="s">
+        <v>40</v>
       </c>
       <c r="I2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
@@ -441,19 +449,19 @@
         <v>45</v>
       </c>
       <c r="F3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G3">
         <v>17.578125</v>
       </c>
-      <c r="H3" s="2">
-        <v>44963.582083333335</v>
+      <c r="H3" t="s">
+        <v>44</v>
       </c>
       <c r="I3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4">
@@ -478,14 +486,14 @@
       <c r="G4">
         <v>27.66009593501628</v>
       </c>
-      <c r="H4" s="2">
-        <v>44969.3205787037</v>
+      <c r="H4" t="s">
+        <v>45</v>
       </c>
       <c r="I4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">
@@ -505,19 +513,19 @@
         <v>44</v>
       </c>
       <c r="F5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G5">
         <v>15.967484395412978</v>
       </c>
-      <c r="H5" s="2">
-        <v>44961.76358796297</v>
+      <c r="H5" t="s">
+        <v>46</v>
       </c>
       <c r="I5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6">
@@ -537,19 +545,19 @@
         <v>45</v>
       </c>
       <c r="F6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G6">
         <v>19.47714681440443</v>
       </c>
-      <c r="H6" s="2">
-        <v>44961.76358796297</v>
+      <c r="H6" t="s">
+        <v>46</v>
       </c>
       <c r="I6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
